--- a/tams-invest-parent/tams-invest-period/src/main/resources/tpl/TrdProjectDuration001.xlsx
+++ b/tams-invest-parent/tams-invest-period/src/main/resources/tpl/TrdProjectDuration001.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\project\tams\tams-invest-parent\tams-invest-period\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\ChongQingTouZi\tams\tams-invest-parent\tams-invest-period\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28245" windowHeight="12615"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28248" windowHeight="12612"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>有效状态</t>
   </si>
@@ -61,10 +61,6 @@
   </si>
   <si>
     <t>实收本息总额</t>
-  </si>
-  <si>
-    <t>合作资产</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -72,22 +68,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
-    <numFmt numFmtId="178" formatCode="#,##0.00000000_ "/>
-    <numFmt numFmtId="179" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="176" formatCode="#,##0.00000000_ "/>
+    <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -119,11 +107,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -428,23 +415,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="3" width="16.75" customWidth="1"/>
-    <col min="4" max="4" width="22.375" customWidth="1"/>
+    <col min="3" max="3" width="16.77734375" customWidth="1"/>
+    <col min="4" max="4" width="22.33203125" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="7" width="19.25" customWidth="1"/>
-    <col min="8" max="8" width="22.75" style="1" customWidth="1"/>
-    <col min="9" max="9" width="21.5" style="1" customWidth="1"/>
-    <col min="10" max="10" width="14.125" style="2" customWidth="1"/>
-    <col min="11" max="14" width="10.875" customWidth="1"/>
-    <col min="15" max="15" width="17.375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.21875" customWidth="1"/>
+    <col min="7" max="7" width="22.77734375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="21.44140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.109375" style="2" customWidth="1"/>
+    <col min="10" max="13" width="10.88671875" customWidth="1"/>
+    <col min="14" max="14" width="17.33203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -463,36 +450,33 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>14</v>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
       <c r="K1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>